--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,6 +1232,113 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122421356</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83255</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norr om Ullstämma, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>539732</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6468455</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>122367322</v>
       </c>
       <c r="B6" t="n">
-        <v>83254</v>
+        <v>83255</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>122367322</v>
       </c>
       <c r="B6" t="n">
-        <v>83255</v>
+        <v>83260</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>122421356</v>
       </c>
       <c r="B7" t="n">
-        <v>83255</v>
+        <v>83260</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>122367322</v>
       </c>
       <c r="B6" t="n">
-        <v>83260</v>
+        <v>83261</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>122421356</v>
       </c>
       <c r="B7" t="n">
-        <v>83260</v>
+        <v>83261</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>122367322</v>
       </c>
       <c r="B6" t="n">
-        <v>83261</v>
+        <v>83262</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,11 +1132,6 @@
       </c>
       <c r="E6" t="n">
         <v>1445</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Bombmurkla</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1237,7 +1232,7 @@
         <v>122421356</v>
       </c>
       <c r="B7" t="n">
-        <v>83261</v>
+        <v>83262</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,11 +1246,6 @@
       </c>
       <c r="E7" t="n">
         <v>1445</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Bombmurkla</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>122367322</v>
       </c>
       <c r="B6" t="n">
-        <v>83262</v>
+        <v>83266</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,6 +1132,11 @@
       </c>
       <c r="E6" t="n">
         <v>1445</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1232,7 +1237,7 @@
         <v>122421356</v>
       </c>
       <c r="B7" t="n">
-        <v>83262</v>
+        <v>83266</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,6 +1251,11 @@
       </c>
       <c r="E7" t="n">
         <v>1445</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>122367322</v>
       </c>
       <c r="B6" t="n">
-        <v>83266</v>
+        <v>83267</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>122421356</v>
       </c>
       <c r="B7" t="n">
-        <v>83266</v>
+        <v>83267</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>122367322</v>
       </c>
       <c r="B6" t="n">
-        <v>83267</v>
+        <v>83270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>122421356</v>
       </c>
       <c r="B7" t="n">
-        <v>83267</v>
+        <v>83270</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>122421356</v>
       </c>
       <c r="B7" t="n">
-        <v>83270</v>
+        <v>83372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1339,6 +1339,111 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127936028</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ullabergs NR, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>539781</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6468484</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karin Nyström, Bengt Nyström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>127936028</v>
       </c>
       <c r="B8" t="n">
-        <v>92640</v>
+        <v>92643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>127936028</v>
       </c>
       <c r="B8" t="n">
-        <v>92643</v>
+        <v>92651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>127936028</v>
       </c>
       <c r="B8" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karin Nyström, Bengt Nyström</t>
+          <t>Bengt Nyström, Karin Nyström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,7 +1344,7 @@
         <v>127936028</v>
       </c>
       <c r="B8" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,10 +1439,119 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Nyström, Karin Nyström</t>
+          <t>Karin Nyström, Bengt Nyström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128250406</v>
+      </c>
+      <c r="B9" t="n">
+        <v>83699</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ullaberg, Ullabergs våtmark, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>539726</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6468453</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elsa Waldo</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elsa Waldo</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>127936028</v>
       </c>
       <c r="B8" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>127936028</v>
       </c>
       <c r="B8" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128250406</v>
       </c>
       <c r="B9" t="n">
-        <v>83699</v>
+        <v>83702</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>127936028</v>
       </c>
       <c r="B8" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128250406</v>
       </c>
       <c r="B9" t="n">
-        <v>83702</v>
+        <v>83786</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1344,7 +1344,7 @@
         <v>127936028</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128250406</v>
       </c>
       <c r="B9" t="n">
-        <v>83786</v>
+        <v>83790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>128250406</v>
       </c>
       <c r="B9" t="n">
-        <v>83790</v>
+        <v>83792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>128250406</v>
       </c>
       <c r="B9" t="n">
-        <v>83792</v>
+        <v>83819</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -1449,7 +1449,7 @@
         <v>128250406</v>
       </c>
       <c r="B9" t="n">
-        <v>83819</v>
+        <v>83823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115999930</v>
+        <v>58344544</v>
       </c>
       <c r="B2" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,22 +705,19 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sams ridväg, Ullstämma Norrgård, Ög</t>
+          <t>Ullstämma, syd - Obj 1159, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539726</v>
+        <v>539721</v>
       </c>
       <c r="R2" t="n">
-        <v>6468457</v>
+        <v>6468460</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,12 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2016-03-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2016-03-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Cirka 105-årig barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,38 +763,37 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>barrmatta</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Inga-Lill Petersson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Inga-Lill Petersson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson, Anita Stridvall, Börje H Fagerlind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115954738</v>
+        <v>115844062</v>
       </c>
       <c r="B3" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -818,20 +814,27 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sams ridväg, Ullstämma Norrgård, Landeryd, Ög</t>
+          <t>Ullaberg Linköping, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539725</v>
+        <v>539732</v>
       </c>
       <c r="R3" t="n">
-        <v>6468454</v>
+        <v>6468465</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,17 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,18 +872,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>David Ek</t>
+          <t>Thomas Weissenberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Ek, Matilda Jansson, Marika Sjödin</t>
+          <t>Thomas Weissenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -895,16 +894,11 @@
         <v>115954737</v>
       </c>
       <c r="B4" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -999,19 +993,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116344584</v>
+        <v>115954738</v>
       </c>
       <c r="B5" t="n">
-        <v>83108</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1032,60 +1021,56 @@
           <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sams ridväg, Ullstämma Norrgård, Landeryd, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>539725</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6468454</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Ullaberg, Ög</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>539724</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6468457</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Linköping</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Landeryd</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Vid grupp av gran</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1094,40 +1079,30 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Monica Andersson</t>
+          <t>David Ek</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Monica Andersson</t>
+          <t>David Ek, Matilda Jansson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122367322</v>
+        <v>115999930</v>
       </c>
       <c r="B6" t="n">
-        <v>83270</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1150,29 +1125,25 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ullstämmaskogen, Ög</t>
+          <t>Sams ridväg, Ullstämma Norrgård, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539738</v>
+        <v>539726</v>
       </c>
       <c r="R6" t="n">
-        <v>6468449</v>
+        <v>6468457</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,17 +1167,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På lokalen som upptäcktes 2024.</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,31 +1188,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Jörneskog</t>
+          <t>Inga-Lill Petersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Jörneskog</t>
+          <t>Inga-Lill Petersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122421356</v>
+        <v>116344584</v>
       </c>
       <c r="B7" t="n">
-        <v>83372</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1274,17 +1235,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norr om Ullstämma, Ög</t>
+          <t>Ullaberg, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539732</v>
+        <v>539724</v>
       </c>
       <c r="R7" t="n">
-        <v>6468455</v>
+        <v>6468457</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,12 +1269,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
+          <t>2024-04-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vid grupp av gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,51 +1288,55 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Monica Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Monica Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127936028</v>
+        <v>122285114</v>
       </c>
       <c r="B8" t="n">
-        <v>92766</v>
+        <v>84158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>1445</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1374,19 +1344,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ullabergs NR, Ög</t>
+          <t>Ullaberg, Linköpings kommun, Linköpings kommun, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539781</v>
+        <v>539716</v>
       </c>
       <c r="R8" t="n">
-        <v>6468484</v>
+        <v>6468466</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1413,12 +1387,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,26 +1418,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Janne Moberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karin Nyström, Bengt Nyström</t>
+          <t>Janne Moberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128250406</v>
+        <v>122367322</v>
       </c>
       <c r="B9" t="n">
-        <v>83823</v>
+        <v>84158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1476,7 +1460,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1488,17 +1472,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ullaberg, Ullabergs våtmark, Ög</t>
+          <t>Ullstämmaskogen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539726</v>
+        <v>539738</v>
       </c>
       <c r="R9" t="n">
-        <v>6468453</v>
+        <v>6468449</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1522,12 +1506,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På lokalen som upptäcktes 2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,15 +1532,1198 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Anders Jörneskog</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Jörneskog</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122421355</v>
+      </c>
+      <c r="B10" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norr om Ullstämma, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>539722</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6468459</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122421356</v>
+      </c>
+      <c r="B11" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norr om Ullstämma, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>539732</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6468455</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122432633</v>
+      </c>
+      <c r="B12" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ullaberg, N, Harvestad, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>539726</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6468461</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Två grupper, en med 2 stora och 1 liten, en med 4 relativt små.  Område med avverkade granar i närheten</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bengt Nyström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bengt Nyström, Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122454160</v>
+      </c>
+      <c r="B13" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bomb, Ullaberg, Ullabergs våtmark, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>539727</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6468456</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Göran Friman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Göran Friman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122562361</v>
+      </c>
+      <c r="B14" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bomb, Ullabergs våtmark, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>539727</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6468457</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mari Sandell</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mari Sandell</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123789973</v>
+      </c>
+      <c r="B15" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ullaberg, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>539723</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6468458</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jonathan Börjesson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jonathan Börjesson, Annika  Carlberg , Fritjof Papmehl-Dufay</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128250406</v>
+      </c>
+      <c r="B16" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ullaberg, Ullabergs våtmark, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>539726</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6468453</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Elsa Waldo</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Elsa Waldo</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131586087</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96501</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ullstämmaskogen NR, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>539709</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6468474</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gabriel Johansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gabriel Johansson, Elsa Waldo, Hasse Andersson, Lovisa Hamberg, Lena Lundin Johansson, Oscar Josefsson, Emma Nordenberg, Andreas Mathisen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>56429278</v>
+      </c>
+      <c r="B18" t="n">
+        <v>87375</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ullstämma S, Ullaberg N, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>539706</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6468460</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2015-09-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2015-09-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Pro Natura-inventering (obj. 1159) för Linköpings kommun</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrskog med stort inslag av asp</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anita Stridvall</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anita Stridvall, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127936028</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ullabergs NR, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>539781</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6468484</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karin Nyström, Bengt Nyström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121473055</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ullaberg, Ullabergs våtmark, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>539801</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6468518</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-05-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-05-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Göran Friman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Göran Friman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22040-2023 artfynd.xlsx
+++ b/artfynd/A 22040-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58344544</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115844062</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115954737</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115954738</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115999930</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116344584</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1427,6 +1462,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122285114</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1541,6 +1581,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122367322</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1643,6 +1688,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122421355</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,6 +1795,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122421356</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122432633</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1977,6 +2037,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122454160</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2086,6 +2151,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122562361</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2195,6 +2265,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123789973</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2304,6 +2379,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128250406</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2406,6 +2486,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131586087</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2513,6 +2598,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56429278</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2618,6 +2708,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127936028</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2724,8 +2819,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121473055</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>